--- a/artfynd/A 54319-2025 artfynd.xlsx
+++ b/artfynd/A 54319-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129683528</v>
       </c>
       <c r="B2" t="n">
-        <v>79071</v>
+        <v>79075</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129683522</v>
       </c>
       <c r="B3" t="n">
-        <v>91582</v>
+        <v>91587</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129683526</v>
       </c>
       <c r="B4" t="n">
-        <v>98757</v>
+        <v>98768</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -975,7 +975,7 @@
         <v>129683521</v>
       </c>
       <c r="B5" t="n">
-        <v>91582</v>
+        <v>91587</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 54319-2025 artfynd.xlsx
+++ b/artfynd/A 54319-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129683528</v>
+        <v>129683522</v>
       </c>
       <c r="B2" t="n">
-        <v>79075</v>
+        <v>91588</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>745452</v>
+        <v>745496</v>
       </c>
       <c r="R2" t="n">
-        <v>7088702</v>
+        <v>7088823</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129683522</v>
+        <v>129683528</v>
       </c>
       <c r="B3" t="n">
-        <v>91587</v>
+        <v>79076</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>745496</v>
+        <v>745452</v>
       </c>
       <c r="R3" t="n">
-        <v>7088823</v>
+        <v>7088702</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +872,7 @@
         <v>129683526</v>
       </c>
       <c r="B4" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -975,7 +975,7 @@
         <v>129683521</v>
       </c>
       <c r="B5" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 54319-2025 artfynd.xlsx
+++ b/artfynd/A 54319-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129683522</v>
       </c>
       <c r="B2" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129683528</v>
       </c>
       <c r="B3" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129683526</v>
       </c>
       <c r="B4" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -975,7 +975,7 @@
         <v>129683521</v>
       </c>
       <c r="B5" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 54319-2025 artfynd.xlsx
+++ b/artfynd/A 54319-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129683522</v>
+        <v>129683528</v>
       </c>
       <c r="B2" t="n">
-        <v>91593</v>
+        <v>79081</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>745496</v>
+        <v>745452</v>
       </c>
       <c r="R2" t="n">
-        <v>7088823</v>
+        <v>7088702</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129683528</v>
+        <v>129683522</v>
       </c>
       <c r="B3" t="n">
-        <v>79081</v>
+        <v>91593</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>745452</v>
+        <v>745496</v>
       </c>
       <c r="R3" t="n">
-        <v>7088702</v>
+        <v>7088823</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 54319-2025 artfynd.xlsx
+++ b/artfynd/A 54319-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129683528</v>
+        <v>129683522</v>
       </c>
       <c r="B2" t="n">
-        <v>79081</v>
+        <v>91593</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>745452</v>
+        <v>745496</v>
       </c>
       <c r="R2" t="n">
-        <v>7088702</v>
+        <v>7088823</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129683522</v>
+        <v>129683528</v>
       </c>
       <c r="B3" t="n">
-        <v>91593</v>
+        <v>79081</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>745496</v>
+        <v>745452</v>
       </c>
       <c r="R3" t="n">
-        <v>7088823</v>
+        <v>7088702</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 54319-2025 artfynd.xlsx
+++ b/artfynd/A 54319-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129683522</v>
+        <v>129683528</v>
       </c>
       <c r="B2" t="n">
-        <v>91593</v>
+        <v>79081</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>745496</v>
+        <v>745452</v>
       </c>
       <c r="R2" t="n">
-        <v>7088823</v>
+        <v>7088702</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129683528</v>
+        <v>129683522</v>
       </c>
       <c r="B3" t="n">
-        <v>79081</v>
+        <v>91597</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>745452</v>
+        <v>745496</v>
       </c>
       <c r="R3" t="n">
-        <v>7088702</v>
+        <v>7088823</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +872,7 @@
         <v>129683526</v>
       </c>
       <c r="B4" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -975,7 +975,7 @@
         <v>129683521</v>
       </c>
       <c r="B5" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 54319-2025 artfynd.xlsx
+++ b/artfynd/A 54319-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>129683522</v>
       </c>
       <c r="B3" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129683526</v>
       </c>
       <c r="B4" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -975,7 +975,7 @@
         <v>129683521</v>
       </c>
       <c r="B5" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 54319-2025 artfynd.xlsx
+++ b/artfynd/A 54319-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129683528</v>
+        <v>129683522</v>
       </c>
       <c r="B2" t="n">
-        <v>79081</v>
+        <v>91599</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>745452</v>
+        <v>745496</v>
       </c>
       <c r="R2" t="n">
-        <v>7088702</v>
+        <v>7088823</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129683522</v>
+        <v>129683528</v>
       </c>
       <c r="B3" t="n">
-        <v>91599</v>
+        <v>79081</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>745496</v>
+        <v>745452</v>
       </c>
       <c r="R3" t="n">
-        <v>7088823</v>
+        <v>7088702</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +872,7 @@
         <v>129683526</v>
       </c>
       <c r="B4" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 54319-2025 artfynd.xlsx
+++ b/artfynd/A 54319-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129683522</v>
       </c>
       <c r="B2" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129683528</v>
       </c>
       <c r="B3" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129683526</v>
       </c>
       <c r="B4" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -975,7 +975,7 @@
         <v>129683521</v>
       </c>
       <c r="B5" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 54319-2025 artfynd.xlsx
+++ b/artfynd/A 54319-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129683522</v>
+        <v>129683528</v>
       </c>
       <c r="B2" t="n">
-        <v>91602</v>
+        <v>79087</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>745496</v>
+        <v>745452</v>
       </c>
       <c r="R2" t="n">
-        <v>7088823</v>
+        <v>7088702</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129683528</v>
+        <v>129683522</v>
       </c>
       <c r="B3" t="n">
-        <v>79084</v>
+        <v>91605</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>745452</v>
+        <v>745496</v>
       </c>
       <c r="R3" t="n">
-        <v>7088702</v>
+        <v>7088823</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +872,7 @@
         <v>129683526</v>
       </c>
       <c r="B4" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -975,7 +975,7 @@
         <v>129683521</v>
       </c>
       <c r="B5" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 54319-2025 artfynd.xlsx
+++ b/artfynd/A 54319-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129683528</v>
+        <v>129683522</v>
       </c>
       <c r="B2" t="n">
-        <v>79087</v>
+        <v>91606</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>745452</v>
+        <v>745496</v>
       </c>
       <c r="R2" t="n">
-        <v>7088702</v>
+        <v>7088823</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129683522</v>
+        <v>129683528</v>
       </c>
       <c r="B3" t="n">
-        <v>91605</v>
+        <v>79088</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>745496</v>
+        <v>745452</v>
       </c>
       <c r="R3" t="n">
-        <v>7088823</v>
+        <v>7088702</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +872,7 @@
         <v>129683526</v>
       </c>
       <c r="B4" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -975,7 +975,7 @@
         <v>129683521</v>
       </c>
       <c r="B5" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 54319-2025 artfynd.xlsx
+++ b/artfynd/A 54319-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129683522</v>
       </c>
       <c r="B2" t="n">
-        <v>91606</v>
+        <v>91623</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129683528</v>
       </c>
       <c r="B3" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129683526</v>
       </c>
       <c r="B4" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -975,7 +975,7 @@
         <v>129683521</v>
       </c>
       <c r="B5" t="n">
-        <v>91606</v>
+        <v>91623</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 54319-2025 artfynd.xlsx
+++ b/artfynd/A 54319-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129683522</v>
+        <v>129683521</v>
       </c>
       <c r="B2" t="n">
-        <v>91623</v>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>745496</v>
+        <v>745638</v>
       </c>
       <c r="R2" t="n">
-        <v>7088823</v>
+        <v>7088958</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129683528</v>
+        <v>129683522</v>
       </c>
       <c r="B3" t="n">
-        <v>79089</v>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>745452</v>
+        <v>745496</v>
       </c>
       <c r="R3" t="n">
-        <v>7088702</v>
+        <v>7088823</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129683526</v>
+        <v>129683528</v>
       </c>
       <c r="B4" t="n">
-        <v>98815</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>745503</v>
+        <v>745452</v>
       </c>
       <c r="R4" t="n">
-        <v>7088814</v>
+        <v>7088702</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -942,18 +942,12 @@
           <t>2025-11-12</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Täckte ca 30x30 cm</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -972,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129683521</v>
+        <v>129683526</v>
       </c>
       <c r="B5" t="n">
-        <v>91623</v>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1007,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>745638</v>
+        <v>745503</v>
       </c>
       <c r="R5" t="n">
-        <v>7088958</v>
+        <v>7088814</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1045,12 +1039,18 @@
           <t>2025-11-12</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Täckte ca 30x30 cm</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 54319-2025 artfynd.xlsx
+++ b/artfynd/A 54319-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129683521</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129683522</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129683528</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1066,8 +1086,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129683526</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>